--- a/frontend/public/originals/prd-slitting-blade.xlsx
+++ b/frontend/public/originals/prd-slitting-blade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parth\Desktop\dcrs-orig-wt\frontend\public\originals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FD2FBB-546A-49BB-B3CB-26E337103DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8831CBD5-9341-44D1-ACE6-6127757C3EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,6 +728,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1765,7 +1768,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.39" bottom="0.25" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="10" max="1048575" man="1"/>
   </colBreaks>
